--- a/XII B INFORMATION.xlsx
+++ b/XII B INFORMATION.xlsx
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1396" uniqueCount="727">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1396" uniqueCount="726">
   <si>
     <t>S.NO.</t>
   </si>
@@ -113,9 +113,6 @@
     <t>EMAIL ID</t>
   </si>
   <si>
-    <t>11B</t>
-  </si>
-  <si>
     <t>19</t>
   </si>
   <si>
@@ -1512,9 +1509,6 @@
   </si>
   <si>
     <t>SAVITAMISHRARKT@GMAIL.COM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11B </t>
   </si>
   <si>
     <t>PRIYA KUMARI</t>
@@ -2639,6 +2633,9 @@
   </si>
   <si>
     <t xml:space="preserve">Employee /  Supply Ward Details </t>
+  </si>
+  <si>
+    <t>12B</t>
   </si>
 </sst>
 </file>
@@ -3653,7 +3650,7 @@
   <sheetData>
     <row r="1" spans="1:8" s="98" customFormat="1" ht="21" x14ac:dyDescent="0.5">
       <c r="A1" s="124" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B1" s="124"/>
       <c r="C1" s="124"/>
@@ -3665,7 +3662,7 @@
     </row>
     <row r="2" spans="1:8" s="97" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="107" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B2" s="108"/>
       <c r="C2" s="108"/>
@@ -3680,7 +3677,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="99" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C3" s="99" t="s">
         <v>1</v>
@@ -3692,13 +3689,13 @@
         <v>11</v>
       </c>
       <c r="F3" s="99" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="G3" s="99" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="H3" s="105" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -3712,16 +3709,16 @@
         <v>37239</v>
       </c>
       <c r="D4" s="94" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E4" s="95" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F4" s="100" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="G4" s="95" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="H4" s="106">
         <v>4435</v>
@@ -3738,16 +3735,16 @@
         <v>39076</v>
       </c>
       <c r="D5" s="94" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E5" s="95" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F5" s="100" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="G5" s="95" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="H5" s="106">
         <v>4435</v>
@@ -3764,16 +3761,16 @@
         <v>37253</v>
       </c>
       <c r="D6" s="94" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E6" s="95" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F6" s="100" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="G6" s="95" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="H6" s="106">
         <v>4435</v>
@@ -3790,16 +3787,16 @@
         <v>39007</v>
       </c>
       <c r="D7" s="96" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E7" s="96" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F7" s="101" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="G7" s="96" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="H7" s="106">
         <v>4435</v>
@@ -3816,16 +3813,16 @@
         <v>37181</v>
       </c>
       <c r="D8" s="96" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E8" s="96" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F8" s="102" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="G8" s="96" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="H8" s="106">
         <v>4435</v>
@@ -3839,19 +3836,19 @@
         <v>39</v>
       </c>
       <c r="C9" s="93" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="D9" s="94" t="s">
+        <v>572</v>
+      </c>
+      <c r="E9" s="95" t="s">
         <v>574</v>
       </c>
-      <c r="E9" s="95" t="s">
-        <v>576</v>
-      </c>
       <c r="F9" s="100" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="G9" s="95" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="H9" s="106">
         <v>4435</v>
@@ -3865,19 +3862,19 @@
         <v>40</v>
       </c>
       <c r="C10" s="92" t="s">
+        <v>380</v>
+      </c>
+      <c r="D10" s="94" t="s">
         <v>381</v>
       </c>
-      <c r="D10" s="94" t="s">
-        <v>382</v>
-      </c>
       <c r="E10" s="95" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F10" s="103" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="G10" s="95" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="H10" s="106">
         <v>4435</v>
@@ -3894,16 +3891,16 @@
         <v>38990</v>
       </c>
       <c r="D11" s="94" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E11" s="95" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F11" s="100" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="G11" s="95" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="H11" s="106">
         <v>4435</v>
@@ -3920,16 +3917,16 @@
         <v>38999</v>
       </c>
       <c r="D12" s="94" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E12" s="95" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F12" s="100" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="G12" s="95" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="H12" s="106">
         <v>4435</v>
@@ -3946,16 +3943,16 @@
         <v>37069</v>
       </c>
       <c r="D13" s="94" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="E13" s="95" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F13" s="104" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="G13" s="95" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="H13" s="106">
         <v>4435</v>
@@ -3972,16 +3969,16 @@
         <v>37068</v>
       </c>
       <c r="D14" s="94" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="E14" s="95" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F14" s="100" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="G14" s="95" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="H14" s="106">
         <v>4435</v>
@@ -3998,16 +3995,16 @@
         <v>37143</v>
       </c>
       <c r="D15" s="94" t="s">
+        <v>504</v>
+      </c>
+      <c r="E15" s="95" t="s">
         <v>506</v>
       </c>
-      <c r="E15" s="95" t="s">
-        <v>508</v>
-      </c>
       <c r="F15" s="100" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G15" s="95" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="H15" s="106">
         <v>4435</v>
@@ -4024,16 +4021,16 @@
         <v>37124</v>
       </c>
       <c r="D16" s="94" t="s">
+        <v>540</v>
+      </c>
+      <c r="E16" s="95" t="s">
         <v>542</v>
       </c>
-      <c r="E16" s="95" t="s">
-        <v>544</v>
-      </c>
       <c r="F16" s="100" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="G16" s="95" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="H16" s="106">
         <v>4435</v>
@@ -4103,10 +4100,10 @@
   <sheetData>
     <row r="1" spans="1:32" s="111" customFormat="1" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A1" s="112" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B1" s="112" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C1" s="112" t="s">
         <v>1</v>
@@ -4175,13 +4172,13 @@
         <v>21</v>
       </c>
       <c r="AA1" s="110" t="s">
+        <v>598</v>
+      </c>
+      <c r="AB1" s="110" t="s">
+        <v>599</v>
+      </c>
+      <c r="AC1" s="110" t="s">
         <v>600</v>
-      </c>
-      <c r="AB1" s="110" t="s">
-        <v>601</v>
-      </c>
-      <c r="AC1" s="110" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.35">
@@ -4189,7 +4186,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C2" s="3">
         <v>38954</v>
@@ -4207,64 +4204,64 @@
         <v>39771</v>
       </c>
       <c r="H2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="J2" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="K2" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="L2" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="M2" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="M2" s="7" t="s">
+      <c r="N2" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="N2" s="7" t="s">
+      <c r="O2" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="O2" s="7" t="s">
+      <c r="P2" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="P2" s="7" t="s">
+      <c r="Q2" s="8" t="s">
         <v>31</v>
-      </c>
-      <c r="Q2" s="8" t="s">
-        <v>32</v>
       </c>
       <c r="R2" s="8">
         <v>1</v>
       </c>
       <c r="S2" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="T2" s="9" t="s">
         <v>33</v>
-      </c>
-      <c r="T2" s="9" t="s">
-        <v>34</v>
       </c>
       <c r="U2" s="3">
         <v>3</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W2" s="3">
         <v>0</v>
       </c>
       <c r="X2" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Y2" s="8">
         <v>9598799195</v>
       </c>
       <c r="Z2" s="10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AA2" s="56" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AB2" s="57"/>
       <c r="AC2" s="57"/>
@@ -4275,7 +4272,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C3" s="3">
         <v>40126</v>
@@ -4287,7 +4284,7 @@
         <v>22837855275</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G3" s="5">
         <v>40121</v>
@@ -4299,58 +4296,58 @@
         <v>11</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K3" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="L3" s="7" t="s">
         <v>343</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="M3" s="7" t="s">
         <v>344</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="N3" s="7" t="s">
         <v>345</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="O3" s="7" t="s">
         <v>346</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="P3" s="7" t="s">
         <v>347</v>
       </c>
-      <c r="P3" s="7" t="s">
-        <v>348</v>
-      </c>
       <c r="Q3" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R3" s="8">
         <v>1</v>
       </c>
       <c r="S3" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="T3" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="U3" s="3">
         <v>3</v>
       </c>
       <c r="V3" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W3" s="3">
         <v>0</v>
       </c>
       <c r="X3" s="7" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="Y3" s="8">
         <v>8756958156</v>
       </c>
       <c r="Z3" s="10" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AA3" s="58" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AB3" s="59"/>
       <c r="AC3" s="60"/>
@@ -4361,7 +4358,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C4" s="3">
         <v>40127</v>
@@ -4373,70 +4370,70 @@
         <v>22694052014</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G4" s="5">
         <v>39814</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K4" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="L4" s="7" t="s">
         <v>338</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="M4" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="N4" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="O4" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="M4" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="N4" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="O4" s="7" t="s">
-        <v>340</v>
-      </c>
       <c r="P4" s="7" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="Q4" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R4" s="8">
         <v>1</v>
       </c>
       <c r="S4" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="T4" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="U4" s="3">
         <v>3</v>
       </c>
       <c r="V4" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W4" s="3">
         <v>0</v>
       </c>
       <c r="X4" s="7" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="Y4" s="8">
         <v>9198889355</v>
       </c>
       <c r="Z4" s="10" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AA4" s="58" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AB4" s="59"/>
       <c r="AC4" s="60"/>
@@ -4447,7 +4444,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C5" s="3">
         <v>37212</v>
@@ -4459,70 +4456,70 @@
         <v>21308620363</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G5" s="5">
         <v>39868</v>
       </c>
       <c r="H5" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I5" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="J5" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="K5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="K5" s="7" t="s">
+      <c r="L5" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="L5" s="7" t="s">
+      <c r="M5" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="M5" s="7" t="s">
+      <c r="N5" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="N5" s="7" t="s">
+      <c r="O5" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="O5" s="7" t="s">
+      <c r="P5" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="P5" s="9" t="s">
-        <v>47</v>
-      </c>
       <c r="Q5" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R5" s="8">
         <v>1</v>
       </c>
       <c r="S5" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="T5" s="9" t="s">
         <v>48</v>
-      </c>
-      <c r="T5" s="9" t="s">
-        <v>49</v>
       </c>
       <c r="U5" s="3">
         <v>1</v>
       </c>
       <c r="V5" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W5" s="3">
         <v>0</v>
       </c>
       <c r="X5" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Y5" s="8">
         <v>9140875958</v>
       </c>
       <c r="Z5" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AA5" s="56" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AB5" s="61"/>
       <c r="AC5" s="56"/>
@@ -4533,7 +4530,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C6" s="3">
         <v>37239</v>
@@ -4545,76 +4542,76 @@
         <v>21326918699</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G6" s="5">
         <v>39939</v>
       </c>
       <c r="H6" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="I6" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="J6" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="K6" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="J6" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="K6" s="12" t="s">
+      <c r="L6" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="L6" s="7" t="s">
+      <c r="M6" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="M6" s="7" t="s">
+      <c r="N6" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="N6" s="7" t="s">
+      <c r="O6" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="O6" s="7" t="s">
+      <c r="P6" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="P6" s="9" t="s">
-        <v>60</v>
-      </c>
       <c r="Q6" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R6" s="8">
         <v>1</v>
       </c>
       <c r="S6" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="T6" s="9" t="s">
         <v>61</v>
-      </c>
-      <c r="T6" s="9" t="s">
-        <v>62</v>
       </c>
       <c r="U6" s="3">
         <v>4</v>
       </c>
       <c r="V6" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="W6" s="3">
         <v>1</v>
       </c>
       <c r="X6" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y6" s="8">
         <v>7985412595</v>
       </c>
       <c r="Z6" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AA6" s="56" t="s">
+        <v>602</v>
+      </c>
+      <c r="AB6" s="62" t="s">
+        <v>603</v>
+      </c>
+      <c r="AC6" s="56" t="s">
         <v>604</v>
-      </c>
-      <c r="AB6" s="62" t="s">
-        <v>605</v>
-      </c>
-      <c r="AC6" s="56" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.35">
@@ -4622,7 +4619,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C7" s="3">
         <v>39030</v>
@@ -4640,70 +4637,70 @@
         <v>39950</v>
       </c>
       <c r="H7" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="K7" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="I7" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="K7" s="9" t="s">
+      <c r="L7" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="L7" s="9" t="s">
+      <c r="M7" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="M7" s="9" t="s">
+      <c r="N7" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="N7" s="9" t="s">
+      <c r="O7" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="O7" s="9" t="s">
+      <c r="P7" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="P7" s="9" t="s">
-        <v>71</v>
-      </c>
       <c r="Q7" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R7" s="8">
         <v>1</v>
       </c>
       <c r="S7" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T7" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="U7" s="3">
         <v>3</v>
       </c>
       <c r="V7" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W7" s="3">
         <v>0</v>
       </c>
       <c r="X7" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Y7" s="8">
         <v>9598422808</v>
       </c>
       <c r="Z7" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AA7" s="56" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AB7" s="61" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="AC7" s="63" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="AF7" s="119"/>
     </row>
@@ -4712,7 +4709,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C8" s="3">
         <v>39056</v>
@@ -4730,64 +4727,64 @@
         <v>40544</v>
       </c>
       <c r="H8" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="J8" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="I8" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="J8" s="6" t="s">
+      <c r="K8" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="K8" s="7" t="s">
+      <c r="L8" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="L8" s="7" t="s">
+      <c r="M8" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="M8" s="14" t="s">
+      <c r="N8" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="N8" s="7" t="s">
+      <c r="O8" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="O8" s="14" t="s">
+      <c r="P8" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="P8" s="9" t="s">
-        <v>82</v>
-      </c>
       <c r="Q8" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R8" s="8">
         <v>1</v>
       </c>
       <c r="S8" s="15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T8" s="15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="U8" s="3">
         <v>3</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W8" s="3">
         <v>0</v>
       </c>
       <c r="X8" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y8" s="3">
         <v>9519725292</v>
       </c>
       <c r="Z8" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA8" s="64" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AB8" s="65"/>
       <c r="AC8" s="64"/>
@@ -4798,7 +4795,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C9" s="3">
         <v>40121</v>
@@ -4810,70 +4807,70 @@
         <v>21327890764</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G9" s="5">
         <v>39448</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K9" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="L9" s="7" t="s">
         <v>328</v>
       </c>
-      <c r="L9" s="7" t="s">
+      <c r="M9" s="7" t="s">
         <v>329</v>
       </c>
-      <c r="M9" s="7" t="s">
+      <c r="N9" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="N9" s="7" t="s">
+      <c r="O9" s="7" t="s">
         <v>331</v>
       </c>
-      <c r="O9" s="7" t="s">
+      <c r="P9" s="7" t="s">
         <v>332</v>
       </c>
-      <c r="P9" s="7" t="s">
-        <v>333</v>
-      </c>
       <c r="Q9" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R9" s="8">
         <v>1</v>
       </c>
       <c r="S9" s="9" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="T9" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="U9" s="3">
         <v>3</v>
       </c>
       <c r="V9" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W9" s="3">
         <v>0</v>
       </c>
       <c r="X9" s="7" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="Y9" s="8">
         <v>8400510565</v>
       </c>
       <c r="Z9" s="10" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AA9" s="58" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AB9" s="59"/>
       <c r="AC9" s="60"/>
@@ -4884,7 +4881,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C10" s="3">
         <v>39032</v>
@@ -4905,67 +4902,67 @@
         <v>20</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J10" s="6">
         <v>2008</v>
       </c>
       <c r="K10" s="84" t="s">
+        <v>86</v>
+      </c>
+      <c r="L10" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="L10" s="9" t="s">
+      <c r="M10" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="M10" s="9" t="s">
+      <c r="N10" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="N10" s="9" t="s">
+      <c r="O10" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="O10" s="9" t="s">
+      <c r="P10" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="P10" s="9" t="s">
-        <v>92</v>
-      </c>
       <c r="Q10" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R10" s="8">
         <v>1</v>
       </c>
       <c r="S10" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="T10" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="U10" s="3">
         <v>3</v>
       </c>
       <c r="V10" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W10" s="3">
         <v>0</v>
       </c>
       <c r="X10" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y10" s="8">
         <v>8090498955</v>
       </c>
       <c r="Z10" s="13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AA10" s="56" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="AB10" s="61" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="AC10" s="63" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="AF10" s="119"/>
     </row>
@@ -4974,7 +4971,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C11" s="8">
         <v>39076</v>
@@ -4986,76 +4983,76 @@
         <v>21052522520</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G11" s="5">
         <v>40544</v>
       </c>
       <c r="H11" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="I11" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="J11" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="I11" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>76</v>
-      </c>
       <c r="K11" s="21" t="s">
+        <v>350</v>
+      </c>
+      <c r="L11" s="15" t="s">
         <v>351</v>
       </c>
-      <c r="L11" s="15" t="s">
+      <c r="M11" s="9" t="s">
         <v>352</v>
       </c>
-      <c r="M11" s="9" t="s">
+      <c r="N11" s="15" t="s">
         <v>353</v>
       </c>
-      <c r="N11" s="15" t="s">
-        <v>354</v>
-      </c>
       <c r="O11" s="9" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="P11" s="15" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="Q11" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R11" s="3">
         <v>1</v>
       </c>
       <c r="S11" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="T11" s="15" t="s">
         <v>33</v>
-      </c>
-      <c r="T11" s="15" t="s">
-        <v>34</v>
       </c>
       <c r="U11" s="3">
         <v>3</v>
       </c>
       <c r="V11" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W11" s="3">
         <v>0</v>
       </c>
       <c r="X11" s="9" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Y11" s="34">
         <v>8858353002</v>
       </c>
       <c r="Z11" s="35" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AA11" s="56" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="AB11" s="89" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="AC11" s="56" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="AF11" s="119"/>
     </row>
@@ -5064,7 +5061,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C12" s="16">
         <v>39096</v>
@@ -5076,70 +5073,70 @@
         <v>21499203466</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G12" s="5">
         <v>40035</v>
       </c>
       <c r="H12" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="I12" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="I12" s="17" t="s">
+      <c r="J12" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="K12" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="J12" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="K12" s="7" t="s">
+      <c r="L12" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="L12" s="7" t="s">
+      <c r="M12" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="M12" s="7" t="s">
+      <c r="N12" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="N12" s="7" t="s">
+      <c r="O12" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="O12" s="7" t="s">
+      <c r="P12" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="P12" s="7" t="s">
-        <v>104</v>
-      </c>
       <c r="Q12" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R12" s="8">
         <v>1</v>
       </c>
       <c r="S12" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="T12" s="9" t="s">
         <v>33</v>
-      </c>
-      <c r="T12" s="9" t="s">
-        <v>34</v>
       </c>
       <c r="U12" s="3">
         <v>3</v>
       </c>
       <c r="V12" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W12" s="3">
         <v>0</v>
       </c>
       <c r="X12" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Y12" s="8">
         <v>9695268145</v>
       </c>
       <c r="Z12" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AA12" s="56" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AB12" s="57"/>
       <c r="AC12" s="57"/>
@@ -5150,7 +5147,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C13" s="3">
         <v>37170</v>
@@ -5168,70 +5165,70 @@
         <v>39517</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I13" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K13" s="85" t="s">
+        <v>108</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="M13" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="J13" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K13" s="85" t="s">
-        <v>109</v>
-      </c>
-      <c r="L13" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="M13" s="7" t="s">
+      <c r="N13" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="N13" s="7" t="s">
+      <c r="O13" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="O13" s="7" t="s">
+      <c r="P13" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="P13" s="9" t="s">
-        <v>123</v>
-      </c>
       <c r="Q13" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R13" s="8">
         <v>1</v>
       </c>
       <c r="S13" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="T13" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="U13" s="3">
         <v>3</v>
       </c>
       <c r="V13" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W13" s="3">
         <v>0</v>
       </c>
       <c r="X13" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y13" s="8">
         <v>7398694084</v>
       </c>
       <c r="Z13" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AA13" s="56" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="AB13" s="61" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="AC13" s="56" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="AF13" s="119"/>
     </row>
@@ -5240,7 +5237,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C14" s="3">
         <v>37217</v>
@@ -5252,70 +5249,70 @@
         <v>21499651012</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G14" s="5">
         <v>39998</v>
       </c>
       <c r="H14" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="K14" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="I14" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="K14" s="7" t="s">
+      <c r="L14" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="L14" s="7" t="s">
+      <c r="M14" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="M14" s="7" t="s">
+      <c r="N14" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="N14" s="7" t="s">
+      <c r="O14" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="O14" s="7" t="s">
+      <c r="P14" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="P14" s="9" t="s">
-        <v>114</v>
-      </c>
       <c r="Q14" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R14" s="8">
         <v>1</v>
       </c>
       <c r="S14" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="T14" s="9" t="s">
         <v>115</v>
-      </c>
-      <c r="T14" s="9" t="s">
-        <v>116</v>
       </c>
       <c r="U14" s="3">
         <v>2</v>
       </c>
       <c r="V14" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
       <c r="X14" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y14" s="8">
         <v>8953295243</v>
       </c>
       <c r="Z14" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AA14" s="56" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AB14" s="61"/>
       <c r="AC14" s="56"/>
@@ -5326,13 +5323,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C15" s="3">
         <v>40147</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E15" s="2">
         <v>21422879109</v>
@@ -5344,64 +5341,64 @@
         <v>40544</v>
       </c>
       <c r="H15" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="J15" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="I15" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="J15" s="6" t="s">
-        <v>76</v>
-      </c>
       <c r="K15" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="L15" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="L15" s="7" t="s">
-        <v>129</v>
-      </c>
       <c r="M15" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="N15" s="7" t="s">
         <v>368</v>
       </c>
-      <c r="N15" s="7" t="s">
+      <c r="O15" s="7" t="s">
         <v>369</v>
       </c>
-      <c r="O15" s="7" t="s">
+      <c r="P15" s="7" t="s">
         <v>370</v>
       </c>
-      <c r="P15" s="7" t="s">
-        <v>371</v>
-      </c>
       <c r="Q15" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R15" s="8">
         <v>1</v>
       </c>
       <c r="S15" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="T15" s="9" t="s">
         <v>33</v>
-      </c>
-      <c r="T15" s="9" t="s">
-        <v>34</v>
       </c>
       <c r="U15" s="3">
         <v>3</v>
       </c>
       <c r="V15" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W15" s="3">
         <v>0</v>
       </c>
       <c r="X15" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="Y15" s="8">
         <v>9651486966</v>
       </c>
       <c r="Z15" s="10" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AA15" s="58" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AB15" s="59"/>
       <c r="AC15" s="60"/>
@@ -5411,7 +5408,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C16" s="3">
         <v>37180</v>
@@ -5429,70 +5426,70 @@
         <v>40138</v>
       </c>
       <c r="H16" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="I16" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="K16" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="I16" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="J16" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="K16" s="9" t="s">
+      <c r="L16" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="L16" s="15" t="s">
+      <c r="M16" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="M16" s="9" t="s">
+      <c r="N16" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="N16" s="15" t="s">
+      <c r="O16" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="O16" s="9" t="s">
+      <c r="P16" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="P16" s="15" t="s">
-        <v>137</v>
-      </c>
       <c r="Q16" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R16" s="8">
         <v>1</v>
       </c>
       <c r="S16" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="T16" s="9" t="s">
         <v>33</v>
-      </c>
-      <c r="T16" s="9" t="s">
-        <v>34</v>
       </c>
       <c r="U16" s="3">
         <v>3</v>
       </c>
       <c r="V16" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W16" s="3">
         <v>0</v>
       </c>
       <c r="X16" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="Y16" s="8">
         <v>9936431332</v>
       </c>
       <c r="Z16" s="13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AA16" s="56" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AB16" s="66" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="AC16" s="56" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="AF16" s="119"/>
     </row>
@@ -5501,7 +5498,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C17" s="3">
         <v>39062</v>
@@ -5519,64 +5516,64 @@
         <v>39752</v>
       </c>
       <c r="H17" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K17" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="I17" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K17" s="7" t="s">
+      <c r="L17" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="L17" s="7" t="s">
+      <c r="M17" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="M17" s="7" t="s">
+      <c r="N17" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="N17" s="7" t="s">
+      <c r="O17" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="O17" s="7" t="s">
+      <c r="P17" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="P17" s="7" t="s">
-        <v>146</v>
-      </c>
       <c r="Q17" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R17" s="8">
         <v>1</v>
       </c>
       <c r="S17" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="T17" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="U17" s="3">
         <v>3</v>
       </c>
       <c r="V17" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W17" s="3">
         <v>0</v>
       </c>
       <c r="X17" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="Y17" s="8">
         <v>7054291240</v>
       </c>
       <c r="Z17" s="19" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AA17" s="56" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AB17" s="57"/>
       <c r="AC17" s="57"/>
@@ -5587,7 +5584,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C18" s="3">
         <v>39020</v>
@@ -5599,70 +5596,70 @@
         <v>21065800616</v>
       </c>
       <c r="F18" s="20" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G18" s="5">
         <v>40014</v>
       </c>
       <c r="H18" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="K18" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="I18" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="J18" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="K18" s="7" t="s">
+      <c r="L18" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="L18" s="7" t="s">
+      <c r="M18" s="14" t="s">
         <v>155</v>
       </c>
-      <c r="M18" s="14" t="s">
+      <c r="N18" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="N18" s="7" t="s">
+      <c r="O18" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="O18" s="14" t="s">
+      <c r="P18" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="P18" s="9" t="s">
-        <v>159</v>
-      </c>
       <c r="Q18" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R18" s="8">
         <v>1</v>
       </c>
       <c r="S18" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="T18" s="15" t="s">
         <v>33</v>
-      </c>
-      <c r="T18" s="15" t="s">
-        <v>34</v>
       </c>
       <c r="U18" s="3">
         <v>3</v>
       </c>
       <c r="V18" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W18" s="3">
         <v>0</v>
       </c>
       <c r="X18" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y18" s="3">
         <v>8081749763</v>
       </c>
       <c r="Z18" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AA18" s="64" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AB18" s="65"/>
       <c r="AC18" s="64"/>
@@ -5673,7 +5670,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C19" s="3">
         <v>39070</v>
@@ -5691,64 +5688,64 @@
         <v>40534</v>
       </c>
       <c r="H19" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="I19" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="I19" s="6" t="s">
+      <c r="J19" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="J19" s="6" t="s">
+      <c r="K19" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="K19" s="7" t="s">
+      <c r="L19" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="L19" s="7" t="s">
+      <c r="M19" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="M19" s="7" t="s">
+      <c r="N19" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="N19" s="7" t="s">
+      <c r="O19" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="O19" s="7" t="s">
+      <c r="P19" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="P19" s="7" t="s">
-        <v>169</v>
-      </c>
       <c r="Q19" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R19" s="8">
         <v>1</v>
       </c>
       <c r="S19" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="T19" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="U19" s="3">
         <v>4</v>
       </c>
       <c r="V19" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W19" s="3">
         <v>0</v>
       </c>
       <c r="X19" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y19" s="8">
         <v>9452636920</v>
       </c>
       <c r="Z19" s="10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AA19" s="56" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AB19" s="57"/>
       <c r="AC19" s="57"/>
@@ -5759,7 +5756,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C20" s="3">
         <v>37224</v>
@@ -5771,70 +5768,70 @@
         <v>21325384557</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G20" s="5">
         <v>39949</v>
       </c>
       <c r="H20" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="K20" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="I20" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="J20" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="K20" s="7" t="s">
+      <c r="L20" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="L20" s="7" t="s">
+      <c r="M20" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="M20" s="7" t="s">
+      <c r="N20" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="N20" s="7" t="s">
+      <c r="O20" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="O20" s="7" t="s">
+      <c r="P20" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="P20" s="7" t="s">
-        <v>180</v>
-      </c>
       <c r="Q20" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R20" s="8">
         <v>1</v>
       </c>
       <c r="S20" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="T20" s="9" t="s">
         <v>61</v>
-      </c>
-      <c r="T20" s="9" t="s">
-        <v>62</v>
       </c>
       <c r="U20" s="3">
         <v>4</v>
       </c>
       <c r="V20" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="W20" s="3">
         <v>1</v>
       </c>
       <c r="X20" s="7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y20" s="8">
         <v>8853120790</v>
       </c>
       <c r="Z20" s="19" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AA20" s="56" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AB20" s="61"/>
       <c r="AC20" s="63"/>
@@ -5845,7 +5842,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C21" s="3">
         <v>37253</v>
@@ -5863,70 +5860,70 @@
         <v>39594</v>
       </c>
       <c r="H21" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K21" s="21" t="s">
         <v>183</v>
       </c>
-      <c r="I21" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="J21" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K21" s="21" t="s">
+      <c r="L21" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="L21" s="9" t="s">
+      <c r="M21" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="M21" s="9" t="s">
+      <c r="N21" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="N21" s="9" t="s">
+      <c r="O21" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="O21" s="9" t="s">
+      <c r="P21" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="P21" s="9" t="s">
-        <v>189</v>
-      </c>
       <c r="Q21" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R21" s="8">
         <v>1</v>
       </c>
       <c r="S21" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="T21" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="U21" s="3">
         <v>3</v>
       </c>
       <c r="V21" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W21" s="3">
         <v>0</v>
       </c>
       <c r="X21" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Y21" s="8">
         <v>9125374243</v>
       </c>
       <c r="Z21" s="13" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AA21" s="56" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="AB21" s="88" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="AC21" s="56" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="22" spans="1:32" x14ac:dyDescent="0.35">
@@ -5934,7 +5931,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C22" s="3">
         <v>38924</v>
@@ -5952,70 +5949,70 @@
         <v>39545</v>
       </c>
       <c r="H22" s="18" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I22" s="18" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J22" s="22">
         <v>2008</v>
       </c>
       <c r="K22" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="L22" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="L22" s="9" t="s">
+      <c r="M22" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="M22" s="9" t="s">
+      <c r="N22" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="N22" s="9" t="s">
+      <c r="O22" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="O22" s="9" t="s">
+      <c r="P22" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="P22" s="9" t="s">
-        <v>198</v>
-      </c>
       <c r="Q22" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R22" s="8">
         <v>1</v>
       </c>
       <c r="S22" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="T22" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="U22" s="3">
         <v>3</v>
       </c>
       <c r="V22" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W22" s="3">
         <v>0</v>
       </c>
       <c r="X22" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Y22" s="8">
         <v>9918420798</v>
       </c>
       <c r="Z22" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AA22" s="56" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AB22" s="66" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="AC22" s="56" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="AF22" s="119"/>
     </row>
@@ -6024,7 +6021,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C23" s="3">
         <v>40139</v>
@@ -6036,70 +6033,70 @@
         <v>21184653009</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G23" s="5">
         <v>39814</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K23" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="L23" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="L23" s="7" t="s">
+      <c r="M23" s="7" t="s">
         <v>359</v>
       </c>
-      <c r="M23" s="7" t="s">
+      <c r="N23" s="7" t="s">
         <v>360</v>
       </c>
-      <c r="N23" s="7" t="s">
+      <c r="O23" s="7" t="s">
         <v>361</v>
       </c>
-      <c r="O23" s="7" t="s">
+      <c r="P23" s="7" t="s">
         <v>362</v>
       </c>
-      <c r="P23" s="7" t="s">
-        <v>363</v>
-      </c>
       <c r="Q23" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R23" s="8">
         <v>1</v>
       </c>
       <c r="S23" s="9" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="T23" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="U23" s="3">
         <v>3</v>
       </c>
       <c r="V23" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W23" s="3">
         <v>0</v>
       </c>
       <c r="X23" s="7" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="Y23" s="8">
         <v>7347759011</v>
       </c>
       <c r="Z23" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AA23" s="58" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AB23" s="59"/>
       <c r="AC23" s="60"/>
@@ -6110,7 +6107,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C24" s="3">
         <v>39033</v>
@@ -6131,67 +6128,67 @@
         <v>26</v>
       </c>
       <c r="I24" s="18" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J24" s="22">
         <v>2008</v>
       </c>
       <c r="K24" s="84" t="s">
+        <v>201</v>
+      </c>
+      <c r="L24" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="L24" s="9" t="s">
+      <c r="M24" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="M24" s="9" t="s">
+      <c r="N24" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="N24" s="9" t="s">
+      <c r="O24" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="O24" s="9" t="s">
+      <c r="P24" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="P24" s="9" t="s">
-        <v>207</v>
-      </c>
       <c r="Q24" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R24" s="8">
         <v>1</v>
       </c>
       <c r="S24" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="T24" s="9" t="s">
         <v>33</v>
-      </c>
-      <c r="T24" s="9" t="s">
-        <v>34</v>
       </c>
       <c r="U24" s="3">
         <v>3</v>
       </c>
       <c r="V24" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W24" s="3">
         <v>0</v>
       </c>
       <c r="X24" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Y24" s="8">
         <v>9026392776</v>
       </c>
       <c r="Z24" s="13" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AA24" s="56" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="AB24" s="66" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="AC24" s="56" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="AF24" s="119"/>
     </row>
@@ -6200,7 +6197,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C25" s="3">
         <v>37228</v>
@@ -6212,70 +6209,70 @@
         <v>21607635206</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G25" s="5">
         <v>39780</v>
       </c>
       <c r="H25" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K25" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="I25" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="J25" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K25" s="7" t="s">
+      <c r="L25" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="L25" s="7" t="s">
+      <c r="M25" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="M25" s="7" t="s">
+      <c r="N25" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="N25" s="7" t="s">
+      <c r="O25" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="O25" s="7" t="s">
+      <c r="P25" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="P25" s="7" t="s">
-        <v>217</v>
-      </c>
       <c r="Q25" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R25" s="8">
         <v>1</v>
       </c>
       <c r="S25" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="T25" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="U25" s="3">
         <v>4</v>
       </c>
       <c r="V25" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W25" s="3">
         <v>0</v>
       </c>
       <c r="X25" s="7" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Y25" s="8">
         <v>7275130076</v>
       </c>
       <c r="Z25" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AA25" s="56" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AB25" s="61"/>
       <c r="AC25" s="63"/>
@@ -6286,7 +6283,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C26" s="16">
         <v>37281</v>
@@ -6298,70 +6295,70 @@
         <v>21416650253</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G26" s="5">
         <v>40341</v>
       </c>
       <c r="H26" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="J26" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="I26" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="J26" s="6" t="s">
-        <v>163</v>
-      </c>
       <c r="K26" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="L26" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="L26" s="7" t="s">
+      <c r="M26" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="M26" s="7" t="s">
+      <c r="N26" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="N26" s="7" t="s">
+      <c r="O26" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="O26" s="7" t="s">
+      <c r="P26" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="P26" s="7" t="s">
-        <v>227</v>
-      </c>
       <c r="Q26" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R26" s="8">
         <v>1</v>
       </c>
       <c r="S26" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="T26" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="U26" s="3">
         <v>3</v>
       </c>
       <c r="V26" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W26" s="3">
         <v>0</v>
       </c>
       <c r="X26" s="7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y26" s="8">
         <v>7052466964</v>
       </c>
       <c r="Z26" s="10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AA26" s="56" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AB26" s="61"/>
       <c r="AC26" s="63"/>
@@ -6372,7 +6369,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C27" s="3">
         <v>37232</v>
@@ -6384,70 +6381,70 @@
         <v>21373952980</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G27" s="5">
         <v>40439</v>
       </c>
       <c r="H27" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="I27" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="I27" s="6" t="s">
-        <v>127</v>
-      </c>
       <c r="J27" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K27" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="L27" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="L27" s="7" t="s">
+      <c r="M27" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="M27" s="7" t="s">
+      <c r="N27" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="N27" s="7" t="s">
+      <c r="O27" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="O27" s="7" t="s">
+      <c r="P27" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="P27" s="7" t="s">
-        <v>236</v>
-      </c>
       <c r="Q27" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R27" s="8">
         <v>1</v>
       </c>
       <c r="S27" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="T27" s="9" t="s">
         <v>33</v>
-      </c>
-      <c r="T27" s="9" t="s">
-        <v>34</v>
       </c>
       <c r="U27" s="3">
         <v>3</v>
       </c>
       <c r="V27" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W27" s="3">
         <v>0</v>
       </c>
       <c r="X27" s="7" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="Y27" s="8">
         <v>9936431332</v>
       </c>
       <c r="Z27" s="10" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AA27" s="56" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AB27" s="61"/>
       <c r="AC27" s="63"/>
@@ -6458,7 +6455,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C28" s="3">
         <v>39007</v>
@@ -6479,67 +6476,67 @@
         <v>13</v>
       </c>
       <c r="I28" s="25" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J28" s="25">
         <v>2008</v>
       </c>
       <c r="K28" s="26" t="s">
+        <v>238</v>
+      </c>
+      <c r="L28" s="27" t="s">
         <v>239</v>
       </c>
-      <c r="L28" s="27" t="s">
+      <c r="M28" s="27" t="s">
         <v>240</v>
       </c>
-      <c r="M28" s="27" t="s">
+      <c r="N28" s="27" t="s">
         <v>241</v>
       </c>
-      <c r="N28" s="27" t="s">
+      <c r="O28" s="27" t="s">
         <v>242</v>
       </c>
-      <c r="O28" s="27" t="s">
+      <c r="P28" s="27" t="s">
         <v>243</v>
       </c>
-      <c r="P28" s="27" t="s">
-        <v>244</v>
-      </c>
       <c r="Q28" s="28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R28" s="8">
         <v>1</v>
       </c>
       <c r="S28" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="T28" s="27" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="U28" s="3">
         <v>4</v>
       </c>
       <c r="V28" s="29" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W28" s="3">
         <v>0</v>
       </c>
       <c r="X28" s="27" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Y28" s="28">
         <v>9452863359</v>
       </c>
       <c r="Z28" s="30" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="AA28" s="67" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="AB28" s="68" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="AC28" s="67" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="29" spans="1:32" x14ac:dyDescent="0.35">
@@ -6547,7 +6544,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C29" s="3">
         <v>37260</v>
@@ -6565,70 +6562,70 @@
         <v>39792</v>
       </c>
       <c r="H29" s="25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I29" s="25" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J29" s="25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K29" s="27" t="s">
+        <v>247</v>
+      </c>
+      <c r="L29" s="27" t="s">
         <v>248</v>
       </c>
-      <c r="L29" s="27" t="s">
+      <c r="M29" s="27" t="s">
         <v>249</v>
       </c>
-      <c r="M29" s="27" t="s">
+      <c r="N29" s="27" t="s">
         <v>250</v>
       </c>
-      <c r="N29" s="27" t="s">
+      <c r="O29" s="27" t="s">
         <v>251</v>
       </c>
-      <c r="O29" s="27" t="s">
+      <c r="P29" s="27" t="s">
         <v>252</v>
       </c>
-      <c r="P29" s="27" t="s">
-        <v>253</v>
-      </c>
       <c r="Q29" s="28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R29" s="8">
         <v>1</v>
       </c>
       <c r="S29" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="T29" s="27" t="s">
         <v>33</v>
-      </c>
-      <c r="T29" s="27" t="s">
-        <v>34</v>
       </c>
       <c r="U29" s="3">
         <v>3</v>
       </c>
       <c r="V29" s="29" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W29" s="3">
         <v>0</v>
       </c>
       <c r="X29" s="27" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Y29" s="28">
         <v>9918881937</v>
       </c>
       <c r="Z29" s="31" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AA29" s="67" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AB29" s="69" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="AC29" s="70" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="AF29" s="119"/>
     </row>
@@ -6637,7 +6634,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C30" s="29">
         <v>37242</v>
@@ -6655,70 +6652,70 @@
         <v>39996</v>
       </c>
       <c r="H30" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="I30" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="J30" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="I30" s="25" t="s">
-        <v>86</v>
-      </c>
-      <c r="J30" s="25" t="s">
-        <v>41</v>
-      </c>
       <c r="K30" s="86" t="s">
+        <v>255</v>
+      </c>
+      <c r="L30" s="27" t="s">
         <v>256</v>
       </c>
-      <c r="L30" s="27" t="s">
+      <c r="M30" s="27" t="s">
         <v>257</v>
       </c>
-      <c r="M30" s="27" t="s">
+      <c r="N30" s="27" t="s">
         <v>258</v>
       </c>
-      <c r="N30" s="27" t="s">
+      <c r="O30" s="27" t="s">
         <v>259</v>
       </c>
-      <c r="O30" s="27" t="s">
-        <v>260</v>
-      </c>
       <c r="P30" s="27" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Q30" s="28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R30" s="8">
         <v>1</v>
       </c>
       <c r="S30" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="T30" s="27" t="s">
         <v>48</v>
-      </c>
-      <c r="T30" s="27" t="s">
-        <v>49</v>
       </c>
       <c r="U30" s="3">
         <v>1</v>
       </c>
       <c r="V30" s="29" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W30" s="3">
         <v>0</v>
       </c>
       <c r="X30" s="27" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="Y30" s="28">
         <v>9519722384</v>
       </c>
       <c r="Z30" s="30" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AA30" s="67" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="AB30" s="69" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="AC30" s="70" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="AF30" s="119"/>
     </row>
@@ -6727,7 +6724,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C31" s="3">
         <v>37181</v>
@@ -6745,70 +6742,70 @@
         <v>39912</v>
       </c>
       <c r="H31" s="25" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I31" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J31" s="25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K31" s="26" t="s">
+        <v>262</v>
+      </c>
+      <c r="L31" s="27" t="s">
         <v>263</v>
       </c>
-      <c r="L31" s="27" t="s">
+      <c r="M31" s="27" t="s">
         <v>264</v>
       </c>
-      <c r="M31" s="27" t="s">
+      <c r="N31" s="27" t="s">
         <v>265</v>
       </c>
-      <c r="N31" s="27" t="s">
+      <c r="O31" s="27" t="s">
         <v>266</v>
       </c>
-      <c r="O31" s="27" t="s">
+      <c r="P31" s="27" t="s">
         <v>267</v>
       </c>
-      <c r="P31" s="27" t="s">
-        <v>268</v>
-      </c>
       <c r="Q31" s="28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R31" s="8">
         <v>1</v>
       </c>
       <c r="S31" s="27" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="T31" s="27" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="U31" s="3">
         <v>3</v>
       </c>
       <c r="V31" s="29" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W31" s="3">
         <v>0</v>
       </c>
       <c r="X31" s="27" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Y31" s="28">
         <v>8858125721</v>
       </c>
       <c r="Z31" s="32" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AA31" s="67" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="AB31" s="87" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC31" s="67" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="32" spans="1:32" x14ac:dyDescent="0.35">
@@ -6816,7 +6813,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C32" s="3">
         <v>37746</v>
@@ -6828,70 +6825,70 @@
         <v>21504052054</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G32" s="5">
         <v>40223</v>
       </c>
       <c r="H32" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="K32" s="7" t="s">
         <v>272</v>
       </c>
-      <c r="I32" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="J32" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="K32" s="7" t="s">
+      <c r="L32" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="L32" s="7" t="s">
+      <c r="M32" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="M32" s="7" t="s">
+      <c r="N32" s="7" t="s">
         <v>275</v>
       </c>
-      <c r="N32" s="7" t="s">
+      <c r="O32" s="7" t="s">
         <v>276</v>
       </c>
-      <c r="O32" s="7" t="s">
+      <c r="P32" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="P32" s="7" t="s">
-        <v>278</v>
-      </c>
       <c r="Q32" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R32" s="8">
         <v>1</v>
       </c>
       <c r="S32" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="T32" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="U32" s="3">
         <v>4</v>
       </c>
       <c r="V32" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
       <c r="X32" s="7" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="Y32" s="8">
         <v>9125091601</v>
       </c>
       <c r="Z32" s="10" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AA32" s="56" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AB32" s="71"/>
       <c r="AC32" s="63"/>
@@ -6902,7 +6899,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C33" s="3">
         <v>39029</v>
@@ -6923,67 +6920,67 @@
         <v>14</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J33" s="6">
         <v>2009</v>
       </c>
       <c r="K33" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="L33" s="7" t="s">
         <v>281</v>
       </c>
-      <c r="L33" s="7" t="s">
+      <c r="M33" s="7" t="s">
         <v>282</v>
       </c>
-      <c r="M33" s="7" t="s">
+      <c r="N33" s="7" t="s">
         <v>283</v>
       </c>
-      <c r="N33" s="7" t="s">
+      <c r="O33" s="7" t="s">
         <v>284</v>
       </c>
-      <c r="O33" s="7" t="s">
+      <c r="P33" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="P33" s="7" t="s">
-        <v>286</v>
-      </c>
       <c r="Q33" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R33" s="8">
         <v>1</v>
       </c>
       <c r="S33" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="T33" s="9" t="s">
         <v>33</v>
-      </c>
-      <c r="T33" s="9" t="s">
-        <v>34</v>
       </c>
       <c r="U33" s="3">
         <v>3</v>
       </c>
       <c r="V33" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W33" s="3">
         <v>0</v>
       </c>
       <c r="X33" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Y33" s="8">
         <v>9305949533</v>
       </c>
       <c r="Z33" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AA33" s="56" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AB33" s="71" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="AC33" s="63" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="AF33" s="119"/>
     </row>
@@ -6992,7 +6989,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C34" s="3">
         <v>37160</v>
@@ -7010,70 +7007,70 @@
         <v>40130</v>
       </c>
       <c r="H34" s="25" t="s">
+        <v>287</v>
+      </c>
+      <c r="I34" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="J34" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="K34" s="27" t="s">
         <v>288</v>
       </c>
-      <c r="I34" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="J34" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="K34" s="27" t="s">
+      <c r="L34" s="27" t="s">
         <v>289</v>
       </c>
-      <c r="L34" s="27" t="s">
+      <c r="M34" s="27" t="s">
         <v>290</v>
       </c>
-      <c r="M34" s="27" t="s">
+      <c r="N34" s="27" t="s">
         <v>291</v>
       </c>
-      <c r="N34" s="27" t="s">
+      <c r="O34" s="27" t="s">
         <v>292</v>
       </c>
-      <c r="O34" s="27" t="s">
+      <c r="P34" s="27" t="s">
         <v>293</v>
       </c>
-      <c r="P34" s="27" t="s">
-        <v>294</v>
-      </c>
       <c r="Q34" s="28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R34" s="8">
         <v>1</v>
       </c>
       <c r="S34" s="27" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="T34" s="27" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="U34" s="3">
         <v>4</v>
       </c>
       <c r="V34" s="29" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W34" s="3">
         <v>0</v>
       </c>
       <c r="X34" s="27" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="Y34" s="28">
         <v>7398773797</v>
       </c>
       <c r="Z34" s="30" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AA34" s="67" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AB34" s="73" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="AC34" s="70" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="AF34" s="119"/>
     </row>
@@ -7082,7 +7079,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C35" s="3">
         <v>38272</v>
@@ -7100,70 +7097,70 @@
         <v>40225</v>
       </c>
       <c r="H35" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I35" s="25" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J35" s="25" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K35" s="27" t="s">
+        <v>297</v>
+      </c>
+      <c r="L35" s="27" t="s">
         <v>298</v>
       </c>
-      <c r="L35" s="27" t="s">
+      <c r="M35" s="27" t="s">
         <v>299</v>
       </c>
-      <c r="M35" s="27" t="s">
+      <c r="N35" s="27" t="s">
         <v>300</v>
       </c>
-      <c r="N35" s="27" t="s">
+      <c r="O35" s="27" t="s">
         <v>301</v>
       </c>
-      <c r="O35" s="27" t="s">
+      <c r="P35" s="27" t="s">
         <v>302</v>
       </c>
-      <c r="P35" s="27" t="s">
-        <v>303</v>
-      </c>
       <c r="Q35" s="28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R35" s="8">
         <v>1</v>
       </c>
       <c r="S35" s="27" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="T35" s="27" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="U35" s="3">
         <v>3</v>
       </c>
       <c r="V35" s="29" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W35" s="3">
         <v>0</v>
       </c>
       <c r="X35" s="27" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="Y35" s="28">
         <v>9721686499</v>
       </c>
       <c r="Z35" s="30" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AA35" s="67" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AB35" s="73" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="AC35" s="70" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="AF35" s="119"/>
     </row>
@@ -7172,7 +7169,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C36" s="3">
         <v>40107</v>
@@ -7184,70 +7181,70 @@
         <v>22650034990</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G36" s="5">
         <v>39938</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K36" s="7" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="L36" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="M36" s="7" t="s">
         <v>319</v>
       </c>
-      <c r="M36" s="7" t="s">
+      <c r="N36" s="7" t="s">
         <v>320</v>
       </c>
-      <c r="N36" s="7" t="s">
+      <c r="O36" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="O36" s="7" t="s">
+      <c r="P36" s="7" t="s">
         <v>322</v>
       </c>
-      <c r="P36" s="7" t="s">
-        <v>323</v>
-      </c>
       <c r="Q36" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R36" s="8">
         <v>1</v>
       </c>
       <c r="S36" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="T36" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="U36" s="3">
         <v>3</v>
       </c>
       <c r="V36" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W36" s="3">
         <v>0</v>
       </c>
       <c r="X36" s="7" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="Y36" s="8">
         <v>6386345720</v>
       </c>
       <c r="Z36" s="10" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AA36" s="58" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AB36" s="72"/>
       <c r="AC36" s="60"/>
@@ -7258,7 +7255,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C37" s="3">
         <v>36488</v>
@@ -7270,70 +7267,70 @@
         <v>21600449694</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G37" s="5">
         <v>39840</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K37" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="L37" s="7" t="s">
         <v>308</v>
       </c>
-      <c r="L37" s="7" t="s">
+      <c r="M37" s="7" t="s">
         <v>309</v>
       </c>
-      <c r="M37" s="7" t="s">
+      <c r="N37" s="7" t="s">
         <v>310</v>
       </c>
-      <c r="N37" s="7" t="s">
+      <c r="O37" s="7" t="s">
         <v>311</v>
       </c>
-      <c r="O37" s="7" t="s">
+      <c r="P37" s="7" t="s">
         <v>312</v>
       </c>
-      <c r="P37" s="7" t="s">
-        <v>313</v>
-      </c>
       <c r="Q37" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R37" s="8">
         <v>1</v>
       </c>
       <c r="S37" s="9" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="T37" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="U37" s="3">
         <v>3</v>
       </c>
       <c r="V37" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W37" s="3">
         <v>0</v>
       </c>
       <c r="X37" s="7" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Y37" s="8">
         <v>7522057072</v>
       </c>
       <c r="Z37" s="10" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AA37" s="58" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AB37" s="59"/>
       <c r="AC37" s="60"/>
@@ -7344,7 +7341,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C38" s="3">
         <v>37156</v>
@@ -7362,64 +7359,64 @@
         <v>39940</v>
       </c>
       <c r="H38" s="18" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I38" s="18" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J38" s="18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K38" s="7" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="L38" s="7" t="s">
+        <v>439</v>
+      </c>
+      <c r="M38" s="7" t="s">
         <v>440</v>
       </c>
-      <c r="M38" s="7" t="s">
+      <c r="N38" s="7" t="s">
         <v>441</v>
       </c>
-      <c r="N38" s="7" t="s">
+      <c r="O38" s="7" t="s">
         <v>442</v>
       </c>
-      <c r="O38" s="7" t="s">
+      <c r="P38" s="7" t="s">
         <v>443</v>
       </c>
-      <c r="P38" s="7" t="s">
-        <v>444</v>
-      </c>
       <c r="Q38" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="R38" s="8">
         <v>2</v>
       </c>
       <c r="S38" s="9" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="T38" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="U38" s="3">
         <v>3</v>
       </c>
       <c r="V38" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W38" s="3">
         <v>0</v>
       </c>
       <c r="X38" s="7" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="Y38" s="8">
         <v>8853767194</v>
       </c>
       <c r="Z38" s="10" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AA38" s="56" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AB38" s="74"/>
       <c r="AC38" s="57"/>
@@ -7430,7 +7427,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C39" s="3">
         <v>38940</v>
@@ -7448,70 +7445,70 @@
         <v>40143</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K39" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="L39" s="9" t="s">
         <v>374</v>
       </c>
-      <c r="L39" s="9" t="s">
+      <c r="M39" s="9" t="s">
         <v>375</v>
       </c>
-      <c r="M39" s="9" t="s">
+      <c r="N39" s="9" t="s">
         <v>376</v>
       </c>
-      <c r="N39" s="9" t="s">
+      <c r="O39" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="P39" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q39" s="8" t="s">
         <v>377</v>
-      </c>
-      <c r="O39" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="P39" s="9" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q39" s="8" t="s">
-        <v>378</v>
       </c>
       <c r="R39" s="8">
         <v>2</v>
       </c>
       <c r="S39" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="T39" s="9" t="s">
         <v>33</v>
-      </c>
-      <c r="T39" s="9" t="s">
-        <v>34</v>
       </c>
       <c r="U39" s="3">
         <v>3</v>
       </c>
       <c r="V39" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W39" s="3">
         <v>0</v>
       </c>
       <c r="X39" s="9" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="Y39" s="8">
         <v>9450320524</v>
       </c>
       <c r="Z39" s="13" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AA39" s="56" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AB39" s="75" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="AC39" s="56" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="AF39" s="119"/>
     </row>
@@ -7520,10 +7517,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C40" s="42" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="D40" s="3">
         <v>1252255738</v>
@@ -7538,70 +7535,70 @@
         <v>39978</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J40" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K40" s="21" t="s">
+        <v>572</v>
+      </c>
+      <c r="L40" s="9" t="s">
+        <v>573</v>
+      </c>
+      <c r="M40" s="9" t="s">
         <v>574</v>
       </c>
-      <c r="L40" s="9" t="s">
+      <c r="N40" s="9" t="s">
         <v>575</v>
       </c>
-      <c r="M40" s="9" t="s">
+      <c r="O40" s="9" t="s">
         <v>576</v>
       </c>
-      <c r="N40" s="9" t="s">
+      <c r="P40" s="9" t="s">
         <v>577</v>
       </c>
-      <c r="O40" s="9" t="s">
-        <v>578</v>
-      </c>
-      <c r="P40" s="9" t="s">
-        <v>579</v>
-      </c>
       <c r="Q40" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="R40" s="8">
         <v>2</v>
       </c>
       <c r="S40" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="T40" s="9" t="s">
         <v>33</v>
-      </c>
-      <c r="T40" s="9" t="s">
-        <v>34</v>
       </c>
       <c r="U40" s="3">
         <v>3</v>
       </c>
       <c r="V40" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W40" s="3">
         <v>0</v>
       </c>
       <c r="X40" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Y40" s="8">
         <v>6394318895</v>
       </c>
       <c r="Z40" s="37" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="AA40" s="56" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="AB40" s="90" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="AC40" s="56" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="41" spans="1:32" x14ac:dyDescent="0.35">
@@ -7609,10 +7606,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D41" s="3">
         <v>1252255756</v>
@@ -7627,70 +7624,70 @@
         <v>40038</v>
       </c>
       <c r="H41" s="18" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I41" s="18" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J41" s="18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K41" s="12" t="s">
+        <v>381</v>
+      </c>
+      <c r="L41" s="7" t="s">
         <v>382</v>
       </c>
-      <c r="L41" s="7" t="s">
+      <c r="M41" s="7" t="s">
         <v>383</v>
       </c>
-      <c r="M41" s="7" t="s">
+      <c r="N41" s="7" t="s">
         <v>384</v>
       </c>
-      <c r="N41" s="7" t="s">
+      <c r="O41" s="7" t="s">
         <v>385</v>
       </c>
-      <c r="O41" s="7" t="s">
+      <c r="P41" s="7" t="s">
         <v>386</v>
       </c>
-      <c r="P41" s="7" t="s">
-        <v>387</v>
-      </c>
       <c r="Q41" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="R41" s="8">
         <v>2</v>
       </c>
       <c r="S41" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="T41" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="U41" s="3">
         <v>4</v>
       </c>
       <c r="V41" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W41" s="3">
         <v>0</v>
       </c>
       <c r="X41" s="7" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="Y41" s="8">
         <v>8423806530</v>
       </c>
       <c r="Z41" s="10" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AA41" s="56" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="AB41" s="76" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="AC41" s="56" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="42" spans="1:32" x14ac:dyDescent="0.35">
@@ -7698,7 +7695,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C42" s="3">
         <v>38990</v>
@@ -7710,76 +7707,76 @@
         <v>21145141686</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G42" s="5">
         <v>40766</v>
       </c>
       <c r="H42" s="18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I42" s="18" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J42" s="18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K42" s="12" t="s">
+        <v>390</v>
+      </c>
+      <c r="L42" s="7" t="s">
         <v>391</v>
       </c>
-      <c r="L42" s="7" t="s">
+      <c r="M42" s="7" t="s">
         <v>392</v>
       </c>
-      <c r="M42" s="7" t="s">
+      <c r="N42" s="7" t="s">
         <v>393</v>
       </c>
-      <c r="N42" s="7" t="s">
+      <c r="O42" s="36" t="s">
         <v>394</v>
       </c>
-      <c r="O42" s="36" t="s">
+      <c r="P42" s="7" t="s">
         <v>395</v>
       </c>
-      <c r="P42" s="7" t="s">
-        <v>396</v>
-      </c>
       <c r="Q42" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="R42" s="8">
         <v>2</v>
       </c>
       <c r="S42" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="T42" s="27" t="s">
         <v>33</v>
-      </c>
-      <c r="T42" s="27" t="s">
-        <v>34</v>
       </c>
       <c r="U42" s="3">
         <v>3</v>
       </c>
       <c r="V42" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W42" s="3">
         <v>0</v>
       </c>
       <c r="X42" s="7" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Y42" s="8">
         <v>9026354036</v>
       </c>
       <c r="Z42" s="19" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AA42" s="56" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="AB42" s="62" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="AC42" s="56" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="43" spans="1:32" x14ac:dyDescent="0.35">
@@ -7787,7 +7784,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C43" s="3">
         <v>37099</v>
@@ -7805,70 +7802,70 @@
         <v>39984</v>
       </c>
       <c r="H43" s="18" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I43" s="18" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J43" s="18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K43" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="L43" s="9" t="s">
         <v>399</v>
       </c>
-      <c r="L43" s="9" t="s">
+      <c r="M43" s="9" t="s">
         <v>400</v>
       </c>
-      <c r="M43" s="9" t="s">
+      <c r="N43" s="9" t="s">
         <v>401</v>
       </c>
-      <c r="N43" s="9" t="s">
+      <c r="O43" s="9" t="s">
         <v>402</v>
       </c>
-      <c r="O43" s="9" t="s">
+      <c r="P43" s="9" t="s">
         <v>403</v>
       </c>
-      <c r="P43" s="9" t="s">
-        <v>404</v>
-      </c>
       <c r="Q43" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="R43" s="8">
         <v>2</v>
       </c>
       <c r="S43" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="T43" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="U43" s="3">
         <v>4</v>
       </c>
       <c r="V43" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W43" s="3">
         <v>0</v>
       </c>
       <c r="X43" s="9" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="Y43" s="8">
         <v>7317677115</v>
       </c>
       <c r="Z43" s="13" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AA43" s="56" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AB43" s="66" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="AC43" s="56" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="AF43" s="119"/>
     </row>
@@ -7877,7 +7874,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C44" s="3">
         <v>37111</v>
@@ -7895,64 +7892,64 @@
         <v>39814</v>
       </c>
       <c r="H44" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I44" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J44" s="18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K44" s="85" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="L44" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="M44" s="7" t="s">
         <v>448</v>
       </c>
-      <c r="M44" s="7" t="s">
+      <c r="N44" s="7" t="s">
         <v>449</v>
       </c>
-      <c r="N44" s="7" t="s">
-        <v>450</v>
-      </c>
       <c r="O44" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="P44" s="7" t="s">
         <v>312</v>
       </c>
-      <c r="P44" s="7" t="s">
-        <v>313</v>
-      </c>
       <c r="Q44" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="R44" s="8">
         <v>2</v>
       </c>
       <c r="S44" s="9" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T44" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="U44" s="3">
         <v>3</v>
       </c>
       <c r="V44" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W44" s="3">
         <v>0</v>
       </c>
       <c r="X44" s="7" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="Y44" s="8">
         <v>8737996950</v>
       </c>
       <c r="Z44" s="10" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AA44" s="57" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="AB44" s="57"/>
       <c r="AC44" s="65"/>
@@ -7963,7 +7960,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C45" s="3">
         <v>38962</v>
@@ -7981,64 +7978,64 @@
         <v>40046</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I45" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J45" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K45" s="84" t="s">
+        <v>406</v>
+      </c>
+      <c r="L45" s="9" t="s">
         <v>407</v>
       </c>
-      <c r="L45" s="9" t="s">
+      <c r="M45" s="9" t="s">
         <v>408</v>
       </c>
-      <c r="M45" s="9" t="s">
+      <c r="N45" s="9" t="s">
         <v>409</v>
       </c>
-      <c r="N45" s="9" t="s">
+      <c r="O45" s="9" t="s">
         <v>410</v>
       </c>
-      <c r="O45" s="9" t="s">
+      <c r="P45" s="9" t="s">
         <v>411</v>
       </c>
-      <c r="P45" s="9" t="s">
-        <v>412</v>
-      </c>
       <c r="Q45" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="R45" s="8">
         <v>2</v>
       </c>
       <c r="S45" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="T45" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="U45" s="3">
         <v>3</v>
       </c>
       <c r="V45" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W45" s="3">
         <v>0</v>
       </c>
       <c r="X45" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Y45" s="8">
         <v>8960963449</v>
       </c>
       <c r="Z45" s="37" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AA45" s="56" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="AB45" s="66"/>
       <c r="AC45" s="56"/>
@@ -8049,7 +8046,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C46" s="3">
         <v>37245</v>
@@ -8067,64 +8064,64 @@
         <v>39995</v>
       </c>
       <c r="H46" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I46" s="18" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J46" s="18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K46" s="7" t="s">
+        <v>413</v>
+      </c>
+      <c r="L46" s="7" t="s">
         <v>414</v>
       </c>
-      <c r="L46" s="7" t="s">
+      <c r="M46" s="7" t="s">
         <v>415</v>
       </c>
-      <c r="M46" s="7" t="s">
+      <c r="N46" s="7" t="s">
         <v>416</v>
       </c>
-      <c r="N46" s="7" t="s">
+      <c r="O46" s="7" t="s">
         <v>417</v>
       </c>
-      <c r="O46" s="7" t="s">
+      <c r="P46" s="7" t="s">
         <v>418</v>
       </c>
-      <c r="P46" s="7" t="s">
-        <v>419</v>
-      </c>
       <c r="Q46" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="R46" s="8">
         <v>2</v>
       </c>
       <c r="S46" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="T46" s="9" t="s">
         <v>33</v>
-      </c>
-      <c r="T46" s="9" t="s">
-        <v>34</v>
       </c>
       <c r="U46" s="3">
         <v>3</v>
       </c>
       <c r="V46" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W46" s="3">
         <v>0</v>
       </c>
       <c r="X46" s="7" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="Y46" s="8">
         <v>9696039630</v>
       </c>
       <c r="Z46" s="10" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AA46" s="56" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AB46" s="56"/>
       <c r="AC46" s="57"/>
@@ -8135,7 +8132,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C47" s="3">
         <v>37743</v>
@@ -8153,70 +8150,70 @@
         <v>39746</v>
       </c>
       <c r="H47" s="18" t="s">
+        <v>421</v>
+      </c>
+      <c r="I47" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="J47" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="K47" s="9" t="s">
         <v>422</v>
       </c>
-      <c r="I47" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="J47" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="K47" s="9" t="s">
+      <c r="L47" s="9" t="s">
         <v>423</v>
       </c>
-      <c r="L47" s="9" t="s">
+      <c r="M47" s="9" t="s">
         <v>424</v>
       </c>
-      <c r="M47" s="9" t="s">
+      <c r="N47" s="9" t="s">
         <v>425</v>
       </c>
-      <c r="N47" s="9" t="s">
+      <c r="O47" s="9" t="s">
         <v>426</v>
       </c>
-      <c r="O47" s="9" t="s">
+      <c r="P47" s="9" t="s">
         <v>427</v>
       </c>
-      <c r="P47" s="9" t="s">
-        <v>428</v>
-      </c>
       <c r="Q47" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="R47" s="8">
         <v>2</v>
       </c>
       <c r="S47" s="9" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="T47" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="U47" s="3">
         <v>3</v>
       </c>
       <c r="V47" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="W47" s="3">
         <v>1</v>
       </c>
       <c r="X47" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Y47" s="8">
         <v>8112876063</v>
       </c>
       <c r="Z47" s="13" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AA47" s="56" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AB47" s="66" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="AC47" s="56" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="AF47" s="119"/>
     </row>
@@ -8225,7 +8222,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C48" s="3">
         <v>37110</v>
@@ -8243,64 +8240,64 @@
         <v>40388</v>
       </c>
       <c r="H48" s="18" t="s">
+        <v>430</v>
+      </c>
+      <c r="I48" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="J48" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="K48" s="85" t="s">
         <v>431</v>
       </c>
-      <c r="I48" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="J48" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="K48" s="85" t="s">
+      <c r="L48" s="7" t="s">
         <v>432</v>
       </c>
-      <c r="L48" s="7" t="s">
+      <c r="M48" s="7" t="s">
         <v>433</v>
       </c>
-      <c r="M48" s="7" t="s">
+      <c r="N48" s="7" t="s">
         <v>434</v>
       </c>
-      <c r="N48" s="7" t="s">
+      <c r="O48" s="7" t="s">
         <v>435</v>
       </c>
-      <c r="O48" s="7" t="s">
+      <c r="P48" s="7" t="s">
         <v>436</v>
       </c>
-      <c r="P48" s="7" t="s">
-        <v>437</v>
-      </c>
       <c r="Q48" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="R48" s="8">
         <v>2</v>
       </c>
       <c r="S48" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="T48" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="U48" s="3">
         <v>4</v>
       </c>
       <c r="V48" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W48" s="3">
         <v>0</v>
       </c>
       <c r="X48" s="7" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="Y48" s="38">
         <v>9451527052</v>
       </c>
       <c r="Z48" s="10" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AA48" s="56" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="AB48" s="56"/>
       <c r="AC48" s="57"/>
@@ -8311,7 +8308,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C49" s="3">
         <v>38999</v>
@@ -8329,70 +8326,70 @@
         <v>40095</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I49" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J49" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K49" s="21" t="s">
+        <v>461</v>
+      </c>
+      <c r="L49" s="9" t="s">
         <v>462</v>
       </c>
-      <c r="L49" s="9" t="s">
+      <c r="M49" s="9" t="s">
         <v>463</v>
       </c>
-      <c r="M49" s="9" t="s">
+      <c r="N49" s="9" t="s">
         <v>464</v>
       </c>
-      <c r="N49" s="9" t="s">
+      <c r="O49" s="9" t="s">
         <v>465</v>
       </c>
-      <c r="O49" s="9" t="s">
+      <c r="P49" s="9" t="s">
         <v>466</v>
       </c>
-      <c r="P49" s="9" t="s">
-        <v>467</v>
-      </c>
       <c r="Q49" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="R49" s="8">
         <v>2</v>
       </c>
       <c r="S49" s="9" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="T49" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="U49" s="3">
         <v>3</v>
       </c>
       <c r="V49" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W49" s="3">
         <v>0</v>
       </c>
       <c r="X49" s="9" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="Y49" s="8">
         <v>9569554818</v>
       </c>
       <c r="Z49" s="37" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AA49" s="56" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="AB49" s="88" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="AC49" s="56" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
     </row>
     <row r="50" spans="1:33" x14ac:dyDescent="0.35">
@@ -8400,7 +8397,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C50" s="3">
         <v>37089</v>
@@ -8418,70 +8415,70 @@
         <v>40374</v>
       </c>
       <c r="H50" s="18" t="s">
+        <v>470</v>
+      </c>
+      <c r="I50" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="J50" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="K50" s="9" t="s">
         <v>471</v>
       </c>
-      <c r="I50" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="J50" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="K50" s="9" t="s">
+      <c r="L50" s="9" t="s">
         <v>472</v>
       </c>
-      <c r="L50" s="9" t="s">
+      <c r="M50" s="9" t="s">
         <v>473</v>
       </c>
-      <c r="M50" s="9" t="s">
+      <c r="N50" s="9" t="s">
         <v>474</v>
       </c>
-      <c r="N50" s="9" t="s">
+      <c r="O50" s="9" t="s">
         <v>475</v>
       </c>
-      <c r="O50" s="9" t="s">
+      <c r="P50" s="9" t="s">
         <v>476</v>
       </c>
-      <c r="P50" s="9" t="s">
-        <v>477</v>
-      </c>
       <c r="Q50" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="R50" s="8">
         <v>2</v>
       </c>
       <c r="S50" s="9" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="T50" s="40" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="U50" s="3">
         <v>3</v>
       </c>
       <c r="V50" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="W50" s="3">
         <v>1</v>
       </c>
       <c r="X50" s="9" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="Y50" s="8">
         <v>8381973787</v>
       </c>
       <c r="Z50" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AA50" s="56" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AB50" s="66" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="AC50" s="56" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="AF50" s="119"/>
     </row>
@@ -8490,7 +8487,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C51" s="3">
         <v>37069</v>
@@ -8508,70 +8505,70 @@
         <v>40096</v>
       </c>
       <c r="H51" s="18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I51" s="18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J51" s="18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K51" s="12" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="L51" s="7" t="s">
+        <v>453</v>
+      </c>
+      <c r="M51" s="7" t="s">
         <v>454</v>
       </c>
-      <c r="M51" s="7" t="s">
+      <c r="N51" s="7" t="s">
         <v>455</v>
       </c>
-      <c r="N51" s="7" t="s">
+      <c r="O51" s="7" t="s">
         <v>456</v>
       </c>
-      <c r="O51" s="7" t="s">
+      <c r="P51" s="7" t="s">
         <v>457</v>
       </c>
-      <c r="P51" s="7" t="s">
-        <v>458</v>
-      </c>
       <c r="Q51" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="R51" s="8">
         <v>2</v>
       </c>
       <c r="S51" s="9" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="T51" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="U51" s="3">
         <v>3</v>
       </c>
       <c r="V51" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W51" s="3">
         <v>0</v>
       </c>
       <c r="X51" s="14" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="Y51" s="39">
         <v>8858162324</v>
       </c>
       <c r="Z51" s="10" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AA51" s="56" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="AB51" s="77" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="AC51" s="56" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="52" spans="1:33" x14ac:dyDescent="0.35">
@@ -8579,7 +8576,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C52" s="3">
         <v>37068</v>
@@ -8597,70 +8594,70 @@
         <v>39597</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="I52" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J52" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K52" s="21" t="s">
+        <v>480</v>
+      </c>
+      <c r="L52" s="9" t="s">
         <v>481</v>
       </c>
-      <c r="L52" s="9" t="s">
+      <c r="M52" s="9" t="s">
         <v>482</v>
       </c>
-      <c r="M52" s="9" t="s">
+      <c r="N52" s="9" t="s">
         <v>483</v>
       </c>
-      <c r="N52" s="9" t="s">
+      <c r="O52" s="9" t="s">
         <v>484</v>
       </c>
-      <c r="O52" s="9" t="s">
+      <c r="P52" s="9" t="s">
         <v>485</v>
       </c>
-      <c r="P52" s="9" t="s">
-        <v>486</v>
-      </c>
       <c r="Q52" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="R52" s="8">
         <v>2</v>
       </c>
       <c r="S52" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="T52" s="40" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="U52" s="3">
         <v>4</v>
       </c>
       <c r="V52" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W52" s="3">
         <v>0</v>
       </c>
       <c r="X52" s="9" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="Y52" s="8">
         <v>8303916454</v>
       </c>
       <c r="Z52" s="37" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AA52" s="56" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="AB52" s="62" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="AC52" s="56" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="53" spans="1:33" x14ac:dyDescent="0.35">
@@ -8668,7 +8665,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C53" s="43">
         <v>40144</v>
@@ -8683,7 +8680,7 @@
         <v>717371580770</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="H53" s="9">
         <v>1</v>
@@ -8695,55 +8692,55 @@
         <v>2011</v>
       </c>
       <c r="K53" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="L53" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="M53" s="2" t="s">
         <v>582</v>
       </c>
-      <c r="L53" s="2" t="s">
+      <c r="N53" s="2" t="s">
         <v>583</v>
       </c>
-      <c r="M53" s="2" t="s">
+      <c r="O53" s="2" t="s">
         <v>584</v>
       </c>
-      <c r="N53" s="2" t="s">
+      <c r="P53" s="2" t="s">
         <v>585</v>
       </c>
-      <c r="O53" s="2" t="s">
-        <v>586</v>
-      </c>
-      <c r="P53" s="2" t="s">
-        <v>587</v>
-      </c>
       <c r="Q53" s="43" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="R53" s="43">
         <v>2</v>
       </c>
       <c r="S53" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="T53" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="T53" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="U53" s="44">
         <v>3</v>
       </c>
       <c r="V53" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W53" s="44">
         <v>0</v>
       </c>
       <c r="X53" s="2" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="Y53" s="43">
         <v>8858775589</v>
       </c>
       <c r="Z53" s="2" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="AA53" s="56" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AB53" s="66"/>
       <c r="AC53" s="56"/>
@@ -8754,7 +8751,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>489</v>
+        <v>725</v>
       </c>
       <c r="C54" s="3">
         <v>37292</v>
@@ -8772,64 +8769,64 @@
         <v>39898</v>
       </c>
       <c r="H54" s="18" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I54" s="18" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J54" s="18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K54" s="9" t="s">
+        <v>488</v>
+      </c>
+      <c r="L54" s="9" t="s">
+        <v>489</v>
+      </c>
+      <c r="M54" s="9" t="s">
         <v>490</v>
       </c>
-      <c r="L54" s="9" t="s">
+      <c r="N54" s="9" t="s">
         <v>491</v>
       </c>
-      <c r="M54" s="9" t="s">
+      <c r="O54" s="9" t="s">
         <v>492</v>
       </c>
-      <c r="N54" s="9" t="s">
+      <c r="P54" s="9" t="s">
         <v>493</v>
       </c>
-      <c r="O54" s="9" t="s">
-        <v>494</v>
-      </c>
-      <c r="P54" s="9" t="s">
-        <v>495</v>
-      </c>
       <c r="Q54" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="R54" s="8">
         <v>2</v>
       </c>
       <c r="S54" s="9" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="T54" s="40" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="U54" s="3">
         <v>3</v>
       </c>
       <c r="V54" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W54" s="3">
         <v>0</v>
       </c>
       <c r="X54" s="9" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="Y54" s="8">
         <v>7905616124</v>
       </c>
       <c r="Z54" s="13" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="AA54" s="56" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AB54" s="66"/>
       <c r="AC54" s="56"/>
@@ -8839,7 +8836,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C55" s="3">
         <v>38284</v>
@@ -8851,70 +8848,70 @@
         <v>21469764215</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="G55" s="5">
         <v>40098</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I55" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J55" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K55" s="9" t="s">
+        <v>498</v>
+      </c>
+      <c r="L55" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="M55" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="N55" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="O55" s="9" t="s">
         <v>500</v>
       </c>
-      <c r="L55" s="9" t="s">
+      <c r="P55" s="9" t="s">
         <v>501</v>
       </c>
-      <c r="M55" s="9" t="s">
-        <v>320</v>
-      </c>
-      <c r="N55" s="9" t="s">
-        <v>321</v>
-      </c>
-      <c r="O55" s="9" t="s">
-        <v>502</v>
-      </c>
-      <c r="P55" s="9" t="s">
-        <v>503</v>
-      </c>
       <c r="Q55" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="R55" s="8">
         <v>2</v>
       </c>
       <c r="S55" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="T55" s="40" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="U55" s="3">
         <v>2</v>
       </c>
       <c r="V55" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W55" s="3">
         <v>0</v>
       </c>
       <c r="X55" s="9" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="Y55" s="8">
         <v>9956993503</v>
       </c>
       <c r="Z55" s="37" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="AA55" s="56" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AB55" s="66"/>
       <c r="AC55" s="56"/>
@@ -8926,7 +8923,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C56" s="3">
         <v>37143</v>
@@ -8944,70 +8941,70 @@
         <v>40005</v>
       </c>
       <c r="H56" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I56" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J56" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K56" s="21" t="s">
+        <v>504</v>
+      </c>
+      <c r="L56" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="M56" s="9" t="s">
         <v>506</v>
       </c>
-      <c r="L56" s="9" t="s">
+      <c r="N56" s="9" t="s">
         <v>507</v>
       </c>
-      <c r="M56" s="9" t="s">
+      <c r="O56" s="9" t="s">
         <v>508</v>
       </c>
-      <c r="N56" s="9" t="s">
+      <c r="P56" s="9" t="s">
         <v>509</v>
       </c>
-      <c r="O56" s="9" t="s">
-        <v>510</v>
-      </c>
-      <c r="P56" s="9" t="s">
-        <v>511</v>
-      </c>
       <c r="Q56" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="R56" s="8">
         <v>2</v>
       </c>
       <c r="S56" s="9" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="T56" s="40" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="U56" s="3">
         <v>4</v>
       </c>
       <c r="V56" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W56" s="3">
         <v>0</v>
       </c>
       <c r="X56" s="9" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="Y56" s="8">
         <v>8707559822</v>
       </c>
       <c r="Z56" s="10" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="AA56" s="56" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="AB56" s="62" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="AC56" s="56" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="57" spans="1:33" x14ac:dyDescent="0.35">
@@ -9015,7 +9012,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C57" s="3">
         <v>38991</v>
@@ -9033,64 +9030,64 @@
         <v>39923</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I57" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J57" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K57" s="9" t="s">
+        <v>513</v>
+      </c>
+      <c r="L57" s="9" t="s">
+        <v>514</v>
+      </c>
+      <c r="M57" s="9" t="s">
         <v>515</v>
       </c>
-      <c r="L57" s="9" t="s">
+      <c r="N57" s="9" t="s">
         <v>516</v>
       </c>
-      <c r="M57" s="9" t="s">
-        <v>517</v>
-      </c>
-      <c r="N57" s="9" t="s">
-        <v>518</v>
-      </c>
       <c r="O57" s="9" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="Q57" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="R57" s="8">
         <v>2</v>
       </c>
       <c r="S57" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="T57" s="40" t="s">
         <v>33</v>
-      </c>
-      <c r="T57" s="40" t="s">
-        <v>34</v>
       </c>
       <c r="U57" s="3">
         <v>3</v>
       </c>
       <c r="V57" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W57" s="3">
         <v>0</v>
       </c>
       <c r="X57" s="9" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="Y57" s="8">
         <v>7307407965</v>
       </c>
       <c r="Z57" s="35" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="AA57" s="56" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AB57" s="66"/>
       <c r="AC57" s="56"/>
@@ -9102,7 +9099,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C58" s="42">
         <v>37124</v>
@@ -9120,70 +9117,70 @@
         <v>40153</v>
       </c>
       <c r="H58" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I58" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J58" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K58" s="21" t="s">
+        <v>540</v>
+      </c>
+      <c r="L58" s="9" t="s">
+        <v>541</v>
+      </c>
+      <c r="M58" s="9" t="s">
         <v>542</v>
       </c>
-      <c r="L58" s="9" t="s">
+      <c r="N58" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="M58" s="9" t="s">
+      <c r="O58" s="9" t="s">
         <v>544</v>
       </c>
-      <c r="N58" s="9" t="s">
+      <c r="P58" s="9" t="s">
         <v>545</v>
       </c>
-      <c r="O58" s="9" t="s">
-        <v>546</v>
-      </c>
-      <c r="P58" s="9" t="s">
-        <v>547</v>
-      </c>
       <c r="Q58" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="R58" s="8">
         <v>2</v>
       </c>
       <c r="S58" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="T58" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="U58" s="3">
         <v>4</v>
       </c>
       <c r="V58" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W58" s="3">
         <v>0</v>
       </c>
       <c r="X58" s="9" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="Y58" s="8">
         <v>8756032421</v>
       </c>
       <c r="Z58" s="37" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="AA58" s="56" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="AB58" s="62" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="AC58" s="56" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="59" spans="1:33" x14ac:dyDescent="0.35">
@@ -9191,7 +9188,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C59" s="3">
         <v>37113</v>
@@ -9209,64 +9206,64 @@
         <v>40155</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I59" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J59" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K59" s="85" t="s">
+        <v>519</v>
+      </c>
+      <c r="L59" s="9" t="s">
+        <v>520</v>
+      </c>
+      <c r="M59" s="9" t="s">
         <v>521</v>
       </c>
-      <c r="L59" s="9" t="s">
+      <c r="N59" s="9" t="s">
         <v>522</v>
       </c>
-      <c r="M59" s="9" t="s">
-        <v>523</v>
-      </c>
-      <c r="N59" s="9" t="s">
-        <v>524</v>
-      </c>
       <c r="O59" s="9" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="Q59" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="R59" s="8">
         <v>2</v>
       </c>
       <c r="S59" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="T59" s="9" t="s">
         <v>33</v>
-      </c>
-      <c r="T59" s="9" t="s">
-        <v>34</v>
       </c>
       <c r="U59" s="3">
         <v>3</v>
       </c>
       <c r="V59" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W59" s="3">
         <v>0</v>
       </c>
       <c r="X59" s="9" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="Y59" s="8">
         <v>9598793218</v>
       </c>
       <c r="Z59" s="37" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="AA59" s="56" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="AB59" s="62"/>
       <c r="AC59" s="56"/>
@@ -9277,7 +9274,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C60" s="3">
         <v>38941</v>
@@ -9295,70 +9292,70 @@
         <v>40504</v>
       </c>
       <c r="H60" s="18" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I60" s="18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J60" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K60" s="9" t="s">
+        <v>525</v>
+      </c>
+      <c r="L60" s="9" t="s">
+        <v>526</v>
+      </c>
+      <c r="M60" s="9" t="s">
         <v>527</v>
       </c>
-      <c r="L60" s="9" t="s">
+      <c r="N60" s="9" t="s">
         <v>528</v>
       </c>
-      <c r="M60" s="9" t="s">
+      <c r="O60" s="9" t="s">
         <v>529</v>
       </c>
-      <c r="N60" s="9" t="s">
+      <c r="P60" s="9" t="s">
         <v>530</v>
       </c>
-      <c r="O60" s="9" t="s">
-        <v>531</v>
-      </c>
-      <c r="P60" s="9" t="s">
-        <v>532</v>
-      </c>
       <c r="Q60" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="R60" s="8">
         <v>2</v>
       </c>
       <c r="S60" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="T60" s="9" t="s">
         <v>48</v>
-      </c>
-      <c r="T60" s="9" t="s">
-        <v>49</v>
       </c>
       <c r="U60" s="3">
         <v>1</v>
       </c>
       <c r="V60" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W60" s="3">
         <v>0</v>
       </c>
       <c r="X60" s="9" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="Y60" s="8">
         <v>9838999245</v>
       </c>
       <c r="Z60" s="13" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="AA60" s="56" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AB60" s="66" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="AC60" s="56" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="AF60" s="119"/>
     </row>
@@ -9367,7 +9364,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>489</v>
+        <v>725</v>
       </c>
       <c r="C61" s="3">
         <v>37293</v>
@@ -9385,64 +9382,64 @@
         <v>39971</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I61" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J61" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K61" s="9" t="s">
+        <v>533</v>
+      </c>
+      <c r="L61" s="9" t="s">
+        <v>534</v>
+      </c>
+      <c r="M61" s="9" t="s">
         <v>535</v>
       </c>
-      <c r="L61" s="9" t="s">
+      <c r="N61" s="9" t="s">
         <v>536</v>
       </c>
-      <c r="M61" s="9" t="s">
+      <c r="O61" s="9" t="s">
         <v>537</v>
       </c>
-      <c r="N61" s="9" t="s">
+      <c r="P61" s="9" t="s">
         <v>538</v>
       </c>
-      <c r="O61" s="9" t="s">
-        <v>539</v>
-      </c>
-      <c r="P61" s="9" t="s">
-        <v>540</v>
-      </c>
       <c r="Q61" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="R61" s="8">
         <v>2</v>
       </c>
       <c r="S61" s="9" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="T61" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="U61" s="3">
         <v>3</v>
       </c>
       <c r="V61" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="W61" s="3">
         <v>1</v>
       </c>
       <c r="X61" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Y61" s="8">
         <v>9250040459</v>
       </c>
       <c r="Z61" s="37" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="AA61" s="56" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AB61" s="66"/>
       <c r="AC61" s="56"/>
@@ -9453,7 +9450,7 @@
         <v>61</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C62" s="3">
         <v>37246</v>
@@ -9471,64 +9468,64 @@
         <v>40209</v>
       </c>
       <c r="H62" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I62" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J62" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K62" s="9" t="s">
+        <v>556</v>
+      </c>
+      <c r="L62" s="9" t="s">
+        <v>557</v>
+      </c>
+      <c r="M62" s="9" t="s">
         <v>558</v>
       </c>
-      <c r="L62" s="9" t="s">
+      <c r="N62" s="9" t="s">
         <v>559</v>
       </c>
-      <c r="M62" s="9" t="s">
+      <c r="O62" s="9" t="s">
         <v>560</v>
       </c>
-      <c r="N62" s="9" t="s">
+      <c r="P62" s="9" t="s">
         <v>561</v>
       </c>
-      <c r="O62" s="9" t="s">
-        <v>562</v>
-      </c>
-      <c r="P62" s="9" t="s">
-        <v>563</v>
-      </c>
       <c r="Q62" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="R62" s="8">
         <v>2</v>
       </c>
       <c r="S62" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="T62" s="9" t="s">
         <v>33</v>
-      </c>
-      <c r="T62" s="9" t="s">
-        <v>34</v>
       </c>
       <c r="U62" s="3">
         <v>3</v>
       </c>
       <c r="V62" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W62" s="3">
         <v>0</v>
       </c>
       <c r="X62" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Y62" s="8">
         <v>9450361868</v>
       </c>
       <c r="Z62" s="37" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="AA62" s="56" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AB62" s="66"/>
       <c r="AC62" s="56"/>
@@ -9539,7 +9536,7 @@
         <v>62</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C63" s="3">
         <v>37072</v>
@@ -9557,64 +9554,64 @@
         <v>40003</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I63" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J63" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K63" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="L63" s="9" t="s">
+        <v>549</v>
+      </c>
+      <c r="M63" s="9" t="s">
         <v>550</v>
       </c>
-      <c r="L63" s="9" t="s">
+      <c r="N63" s="9" t="s">
         <v>551</v>
       </c>
-      <c r="M63" s="9" t="s">
+      <c r="O63" s="9" t="s">
         <v>552</v>
       </c>
-      <c r="N63" s="9" t="s">
+      <c r="P63" s="9" t="s">
         <v>553</v>
       </c>
-      <c r="O63" s="9" t="s">
-        <v>554</v>
-      </c>
-      <c r="P63" s="9" t="s">
-        <v>555</v>
-      </c>
       <c r="Q63" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="R63" s="8">
         <v>2</v>
       </c>
       <c r="S63" s="9" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="T63" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="U63" s="3">
         <v>3</v>
       </c>
       <c r="V63" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="W63" s="3">
         <v>1</v>
       </c>
       <c r="X63" s="9" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="Y63" s="8">
         <v>8318344674</v>
       </c>
       <c r="Z63" s="10" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="AA63" s="56" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AB63" s="66"/>
       <c r="AC63" s="56"/>
@@ -9625,7 +9622,7 @@
         <v>63</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="C64" s="3">
         <v>37118</v>
@@ -9643,64 +9640,64 @@
         <v>39642</v>
       </c>
       <c r="H64" s="9" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I64" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J64" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K64" s="9" t="s">
+        <v>563</v>
+      </c>
+      <c r="L64" s="9" t="s">
+        <v>564</v>
+      </c>
+      <c r="M64" s="9" t="s">
         <v>565</v>
       </c>
-      <c r="L64" s="9" t="s">
+      <c r="N64" s="9" t="s">
         <v>566</v>
       </c>
-      <c r="M64" s="9" t="s">
+      <c r="O64" s="9" t="s">
         <v>567</v>
       </c>
-      <c r="N64" s="9" t="s">
+      <c r="P64" s="9" t="s">
         <v>568</v>
       </c>
-      <c r="O64" s="9" t="s">
-        <v>569</v>
-      </c>
-      <c r="P64" s="9" t="s">
-        <v>570</v>
-      </c>
       <c r="Q64" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="R64" s="8">
         <v>2</v>
       </c>
       <c r="S64" s="9" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="T64" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="U64" s="3">
         <v>3</v>
       </c>
       <c r="V64" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="W64" s="3">
         <v>1</v>
       </c>
       <c r="X64" s="9" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="Y64" s="8">
         <v>8081238677</v>
       </c>
       <c r="Z64" s="10" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="AA64" s="56" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AB64" s="66"/>
       <c r="AC64" s="56"/>
@@ -9849,170 +9846,170 @@
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B2" s="118" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C2" s="118" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B3" s="116" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="C3" s="117" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B4" s="116" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C4" s="117" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B5" s="116" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C5" s="117" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B6" s="116" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C6" s="117" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B7" s="116" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="C7" s="117" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B8" s="116" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="C8" s="117" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B9" s="116" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C9" s="117" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B10" s="116" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="C10" s="117" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B11" s="116" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="C11" s="117" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
     </row>
     <row r="12" spans="2:3" ht="29" x14ac:dyDescent="0.35">
       <c r="B12" s="116" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C12" s="117" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
     </row>
     <row r="13" spans="2:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="116" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="C13" s="117" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
     </row>
     <row r="14" spans="2:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="116" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C14" s="117" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="15" spans="2:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="116" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="C15" s="117" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
     </row>
     <row r="16" spans="2:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="116" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="C16" s="117" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="116" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="C17" s="117" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="116" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="C18" s="117" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="116" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C19" s="117" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B20" s="116" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="C20" s="117" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="116" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="C21" s="117" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
     </row>
     <row r="22" spans="2:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="116" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="C22" s="117" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
     </row>
   </sheetData>
@@ -10032,13 +10029,13 @@
   <sheetData>
     <row r="4" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B4" s="113" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C4" s="113" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D4" s="113" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.35">
@@ -10046,10 +10043,10 @@
         <v>1</v>
       </c>
       <c r="C5" s="115" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="D5" s="125" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.35">
@@ -10057,7 +10054,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="115" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="D6" s="125"/>
     </row>
@@ -10066,10 +10063,10 @@
         <v>3</v>
       </c>
       <c r="C7" s="115" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="D7" s="114" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.35">
@@ -10077,10 +10074,10 @@
         <v>4</v>
       </c>
       <c r="C8" s="115" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="D8" s="114" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.35">
@@ -10088,10 +10085,10 @@
         <v>5</v>
       </c>
       <c r="C9" s="115" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="D9" s="114" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.35">
@@ -10099,10 +10096,10 @@
         <v>6</v>
       </c>
       <c r="C10" s="115" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="D10" s="114" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.35">
@@ -10110,10 +10107,10 @@
         <v>7</v>
       </c>
       <c r="C11" s="115" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="D11" s="114" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.35">
@@ -10121,10 +10118,10 @@
         <v>8</v>
       </c>
       <c r="C12" s="115" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="D12" s="114" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.35">
@@ -10132,10 +10129,10 @@
         <v>9</v>
       </c>
       <c r="C13" s="115" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="D13" s="114" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="14" spans="2:4" ht="29" x14ac:dyDescent="0.35">
@@ -10143,10 +10140,10 @@
         <v>10</v>
       </c>
       <c r="C14" s="115" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="D14" s="114" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.35">
@@ -10154,10 +10151,10 @@
         <v>11</v>
       </c>
       <c r="C15" s="115" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="D15" s="114" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.35">
@@ -10165,10 +10162,10 @@
         <v>12</v>
       </c>
       <c r="C16" s="115" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D16" s="114" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="17" spans="2:4" ht="29" x14ac:dyDescent="0.35">
@@ -10176,10 +10173,10 @@
         <v>13</v>
       </c>
       <c r="C17" s="115" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="D17" s="114" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.35">
@@ -10187,10 +10184,10 @@
         <v>14</v>
       </c>
       <c r="C18" s="115" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="D18" s="114" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.35">
@@ -10198,10 +10195,10 @@
         <v>15</v>
       </c>
       <c r="C19" s="115" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="D19" s="114" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.35">
@@ -10209,10 +10206,10 @@
         <v>16</v>
       </c>
       <c r="C20" s="115" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="D20" s="114" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.35">
@@ -10220,10 +10217,10 @@
         <v>17</v>
       </c>
       <c r="C21" s="115" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="D21" s="114" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
     </row>
     <row r="22" spans="2:4" ht="29" x14ac:dyDescent="0.35">
@@ -10231,10 +10228,10 @@
         <v>18</v>
       </c>
       <c r="C22" s="115" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="D22" s="115" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.35">
@@ -10242,10 +10239,10 @@
         <v>19</v>
       </c>
       <c r="C23" s="115" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="D23" s="115" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
     </row>
     <row r="24" spans="2:4" ht="29" x14ac:dyDescent="0.35">
@@ -10253,10 +10250,10 @@
         <v>20</v>
       </c>
       <c r="C24" s="115" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="D24" s="115" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
     </row>
   </sheetData>
@@ -10283,7 +10280,7 @@
   <sheetData>
     <row r="1" spans="2:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="54" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C1" s="46">
         <v>7</v>
@@ -10298,7 +10295,7 @@
         <v>ANMOL KUMAR</v>
       </c>
       <c r="E2" s="81" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="F2" s="52" t="str">
         <f>VLOOKUP($C$1,'Sheet1 (5)'!A1:AC69,27,0)</f>
@@ -10307,14 +10304,14 @@
     </row>
     <row r="3" spans="2:16" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B3" s="49" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="C3" s="48">
         <f>VLOOKUP($C$1,'Sheet1 (5)'!A1:Z64,3,0)</f>
         <v>39056</v>
       </c>
       <c r="E3" s="81" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F3" s="52">
         <f>VLOOKUP($C$1,'Sheet1 (5)'!A1:AC69,28,0)</f>
@@ -10330,7 +10327,7 @@
         <v>SHIV POOJAN</v>
       </c>
       <c r="E4" s="81" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="F4" s="52">
         <f>VLOOKUP($C$1,'Sheet1 (5)'!A2:AC69,29,0)</f>
@@ -10355,13 +10352,13 @@
         <v>40544</v>
       </c>
       <c r="F6" s="44" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="G6" s="44" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="H6" s="44" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="I6" s="44"/>
     </row>
@@ -10370,13 +10367,13 @@
       <c r="C7" s="48"/>
       <c r="E7" s="83"/>
       <c r="F7" s="44" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G7" s="44" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H7" s="44" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="I7" s="44"/>
     </row>
@@ -10426,13 +10423,13 @@
         <v>awanitk94@gmail.com</v>
       </c>
       <c r="F10" s="44" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G10" s="44" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="H10" s="44" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="I10" s="44"/>
       <c r="P10">
@@ -10443,13 +10440,13 @@
       <c r="B11" s="49"/>
       <c r="C11" s="48"/>
       <c r="F11" s="44" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="G11" s="44" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H11" s="44" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="I11" s="44"/>
       <c r="P11">
@@ -10497,45 +10494,45 @@
     </row>
     <row r="15" spans="2:16" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B15" s="50" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C15" s="52" t="str">
         <f>VLOOKUP($C$1,'Sheet1 (5)'!A1:Z69,20,0)</f>
         <v>OBC</v>
       </c>
       <c r="F15" s="44" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="G15" s="44" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="H15" s="44" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="I15" s="44"/>
     </row>
     <row r="16" spans="2:16" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B16" s="50" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C16" s="52" t="str">
         <f>VLOOKUP($C$1,'Sheet1 (5)'!A1:Z69,19,0)</f>
         <v>RONIYAR</v>
       </c>
       <c r="F16" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G16" s="44" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H16" s="44" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="I16" s="44"/>
     </row>
     <row r="17" spans="2:9" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B17" s="50" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C17" s="52" t="str">
         <f>VLOOKUP($C$1,'Sheet1 (5)'!A1:Z69,17,0)</f>
@@ -10597,7 +10594,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="127" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B1" s="127"/>
       <c r="C1" s="127"/>
@@ -10605,7 +10602,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="126" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="B2" s="126"/>
       <c r="C2" s="126"/>
@@ -10613,16 +10610,16 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="121" t="s">
+        <v>718</v>
+      </c>
+      <c r="B3" s="121" t="s">
+        <v>719</v>
+      </c>
+      <c r="C3" s="121" t="s">
         <v>720</v>
       </c>
-      <c r="B3" s="121" t="s">
+      <c r="D3" s="121" t="s">
         <v>721</v>
-      </c>
-      <c r="C3" s="121" t="s">
-        <v>722</v>
-      </c>
-      <c r="D3" s="121" t="s">
-        <v>723</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -10633,10 +10630,10 @@
         <v>37239</v>
       </c>
       <c r="C4" s="122" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D4" s="122" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -10647,10 +10644,10 @@
         <v>39076</v>
       </c>
       <c r="C5" s="122" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D5" s="122" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -10661,10 +10658,10 @@
         <v>37253</v>
       </c>
       <c r="C6" s="122" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D6" s="122" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -10675,10 +10672,10 @@
         <v>39007</v>
       </c>
       <c r="C7" s="122" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D7" s="122" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -10689,10 +10686,10 @@
         <v>37181</v>
       </c>
       <c r="C8" s="122" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D8" s="122" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -10703,10 +10700,10 @@
         <v>38995</v>
       </c>
       <c r="C9" s="122" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="D9" s="122" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -10717,10 +10714,10 @@
         <v>37070</v>
       </c>
       <c r="C10" s="122" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D10" s="122" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -10731,10 +10728,10 @@
         <v>38990</v>
       </c>
       <c r="C11" s="122" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D11" s="122" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -10745,10 +10742,10 @@
         <v>38999</v>
       </c>
       <c r="C12" s="122" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D12" s="122" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -10759,10 +10756,10 @@
         <v>37069</v>
       </c>
       <c r="C13" s="122" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="D13" s="122" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -10773,10 +10770,10 @@
         <v>37068</v>
       </c>
       <c r="C14" s="122" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D14" s="122" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -10787,10 +10784,10 @@
         <v>37143</v>
       </c>
       <c r="C15" s="122" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="D15" s="122" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -10801,10 +10798,10 @@
         <v>37124</v>
       </c>
       <c r="C16" s="122" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="D16" s="122" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -10815,10 +10812,10 @@
         <v>39032</v>
       </c>
       <c r="C17" s="122" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D17" s="122" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -10829,10 +10826,10 @@
         <v>37170</v>
       </c>
       <c r="C18" s="122" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D18" s="122" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -10843,10 +10840,10 @@
         <v>39033</v>
       </c>
       <c r="C19" s="122" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D19" s="122" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -10857,10 +10854,10 @@
         <v>37242</v>
       </c>
       <c r="C20" s="122" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D20" s="122" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -10871,10 +10868,10 @@
         <v>37111</v>
       </c>
       <c r="C21" s="122" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="D21" s="122" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -10885,10 +10882,10 @@
         <v>38962</v>
       </c>
       <c r="C22" s="122" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D22" s="122" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -10899,10 +10896,10 @@
         <v>37110</v>
       </c>
       <c r="C23" s="122" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D23" s="122" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -10913,10 +10910,10 @@
         <v>37113</v>
       </c>
       <c r="C24" s="122" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="D24" s="122" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
